--- a/data/trans_orig/P04A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023</t>
+          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>29858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55261</t>
+          <t>55304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41288</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70239</t>
+          <t>69603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78056</t>
+          <t>78037</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116600</t>
+          <t>115263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37052</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48325</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73112</t>
+          <t>72045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>38853</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66676</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63174</t>
+          <t>63743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87478</t>
+          <t>85775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122788</t>
+          <t>123924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>348230</t>
+          <t>350037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>386671</t>
+          <t>387179</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>576112</t>
+          <t>573020</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>614589</t>
+          <t>613913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>932930</t>
+          <t>935901</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>991147</t>
+          <t>991689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43775</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51784</t>
+          <t>51681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52492</t>
+          <t>52648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,47 +1653,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>31704</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>21265</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>44635</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>31704</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21526</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>44770</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49248</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87244</t>
+          <t>87730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157569</t>
+          <t>148275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267053</t>
+          <t>268637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216317</t>
+          <t>214628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>507846</t>
+          <t>522532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>422329</t>
+          <t>415747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>754515</t>
+          <t>741720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86478</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162833</t>
+          <t>161468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57519</t>
+          <t>56412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100471</t>
+          <t>99060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160223</t>
+          <t>160979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248045</t>
+          <t>248515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>390787</t>
+          <t>381183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>649135</t>
+          <t>653091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>429015</t>
+          <t>414789</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>647105</t>
+          <t>645932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>905366</t>
+          <t>899894</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1251962</t>
+          <t>1255676</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1171103</t>
+          <t>1170363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1582810</t>
+          <t>1639995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1120825</t>
+          <t>1110319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1500561</t>
+          <t>1498942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2319410</t>
+          <t>2346418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2938174</t>
+          <t>2936883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>843</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51122</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97863</t>
+          <t>98679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42032</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66551</t>
+          <t>66766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99345</t>
+          <t>99588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150624</t>
+          <t>155471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56415</t>
+          <t>59878</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167286</t>
+          <t>170192</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>221304</t>
+          <t>221377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191793</t>
+          <t>194194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233739</t>
+          <t>237478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372684</t>
+          <t>376435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>442512</t>
+          <t>441134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>324041</t>
+          <t>323256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>381324</t>
+          <t>378869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332898</t>
+          <t>332682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377864</t>
+          <t>378001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>668345</t>
+          <t>671759</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>743539</t>
+          <t>742198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54872</t>
+          <t>55644</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36155</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37923</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80377</t>
+          <t>78642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77085</t>
+          <t>78026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36118</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66186</t>
+          <t>64579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80694</t>
+          <t>86267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127910</t>
+          <t>131458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>257781</t>
+          <t>267656</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>383744</t>
+          <t>388821</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321194</t>
+          <t>319185</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>652824</t>
+          <t>638303</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>636355</t>
+          <t>633364</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>954243</t>
+          <t>972797</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>126864</t>
+          <t>130482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207061</t>
+          <t>207236</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107391</t>
+          <t>110723</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159000</t>
+          <t>160553</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>253332</t>
+          <t>258930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>350010</t>
+          <t>352994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>622261</t>
+          <t>639536</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>893108</t>
+          <t>899085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>659780</t>
+          <t>666833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>901749</t>
+          <t>907138</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1417559</t>
+          <t>1413212</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1767157</t>
+          <t>1763702</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1890054</t>
+          <t>1894898</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2364539</t>
+          <t>2315176</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2073131</t>
+          <t>2067130</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2456454</t>
+          <t>2462439</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4030916</t>
+          <t>4017542</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4595904</t>
+          <t>4605931</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>36644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>29166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,49 +858,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6874</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17137</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9808</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5847</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15502</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41932</t>
+          <t>75934</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>59555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55304</t>
+          <t>97635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51731</t>
+          <t>60341</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69603</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>93663</t>
+          <t>136275</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78037</t>
+          <t>115469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115263</t>
+          <t>160748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1064,69 +1064,69 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36589</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>32367</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24228</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42787</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31813</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23952</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41431</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58637</t>
+          <t>60151</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>48142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72045</t>
+          <t>74189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51954</t>
+          <t>51609</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>45427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>103020</t>
+          <t>107970</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85775</t>
+          <t>88369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123924</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>367558</t>
+          <t>391818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>350037</t>
+          <t>368610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>387179</t>
+          <t>415830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>597027</t>
+          <t>644781</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>573020</t>
+          <t>624630</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>613913</t>
+          <t>663780</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>964585</t>
+          <t>1036599</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935901</t>
+          <t>1005620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>991689</t>
+          <t>1068520</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>512437</t>
+          <t>575936</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>512437</t>
+          <t>575936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>512437</t>
+          <t>575936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>752604</t>
+          <t>818537</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>752604</t>
+          <t>818537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>752604</t>
+          <t>818537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1265041</t>
+          <t>1394473</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1265041</t>
+          <t>1394473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1265041</t>
+          <t>1394473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>13578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>46525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>24332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>59593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>38184</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>26472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>53576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>65535</t>
+          <t>73418</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87730</t>
+          <t>91739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>224226</t>
+          <t>324612</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148275</t>
+          <t>284141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268637</t>
+          <t>366892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>298081</t>
+          <t>318148</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214628</t>
+          <t>286380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>522532</t>
+          <t>352353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>522307</t>
+          <t>642759</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>415747</t>
+          <t>593041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>741720</t>
+          <t>695803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1859,67 +1859,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125354</t>
+          <t>116926</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86895</t>
+          <t>92192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161468</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>82606</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>67221</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>100424</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79766</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>56412</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>99060</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>205120</t>
+          <t>199533</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160979</t>
+          <t>169714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248515</t>
+          <t>228665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>562578</t>
+          <t>582704</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>381183</t>
+          <t>532372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>653091</t>
+          <t>630087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>564477</t>
+          <t>615581</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>414789</t>
+          <t>578010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>645932</t>
+          <t>655210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1127055</t>
+          <t>1198285</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>899894</t>
+          <t>1139782</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1255676</t>
+          <t>1265695</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1307015</t>
+          <t>1128062</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1170363</t>
+          <t>1074793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1639995</t>
+          <t>1182495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1248024</t>
+          <t>1100387</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1110319</t>
+          <t>1058573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1498942</t>
+          <t>1146225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2555039</t>
+          <t>2228449</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2346418</t>
+          <t>2157270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2936883</t>
+          <t>2291833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2274023</t>
+          <t>2215897</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2274023</t>
+          <t>2215897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2274023</t>
+          <t>2215897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2231838</t>
+          <t>2163896</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2231838</t>
+          <t>2163896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2231838</t>
+          <t>2163896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4505861</t>
+          <t>4379792</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4505861</t>
+          <t>4379792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4505861</t>
+          <t>4379792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,22 +2315,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67896</t>
+          <t>90969</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>72892</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98679</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52220</t>
+          <t>77221</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>62976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66766</t>
+          <t>94699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>120115</t>
+          <t>168190</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99588</t>
+          <t>144085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>155471</t>
+          <t>196665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -2654,27 +2654,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>33733</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>41565</t>
+          <t>41176</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>55913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>194944</t>
+          <t>203738</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170192</t>
+          <t>174446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>221377</t>
+          <t>231955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>213820</t>
+          <t>228077</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194194</t>
+          <t>209018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237478</t>
+          <t>250632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>408764</t>
+          <t>431814</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>376435</t>
+          <t>396200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>441134</t>
+          <t>469282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>350556</t>
+          <t>381797</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>323256</t>
+          <t>350847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378869</t>
+          <t>409868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>355222</t>
+          <t>389737</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332682</t>
+          <t>366451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378001</t>
+          <t>413668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>705778</t>
+          <t>771534</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671759</t>
+          <t>733843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>742198</t>
+          <t>810778</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>640500</t>
+          <t>705057</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>640500</t>
+          <t>705057</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>640500</t>
+          <t>705057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>655780</t>
+          <t>730007</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>655780</t>
+          <t>730007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>655780</t>
+          <t>730007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1296280</t>
+          <t>1435064</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1296280</t>
+          <t>1435064</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1296280</t>
+          <t>1435064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,102 +3110,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>64049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>19619</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>41935</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>67790</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>48807</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>92391</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>23392</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>14832</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>36527</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>55512</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>38314</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>78642</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78026</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>55216</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>69401</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>106021</t>
+          <t>118804</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86267</t>
+          <t>97588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>131458</t>
+          <t>140567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>334054</t>
+          <t>491515</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>267656</t>
+          <t>447992</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>388821</t>
+          <t>541856</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>402032</t>
+          <t>455709</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>319185</t>
+          <t>415576</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>638303</t>
+          <t>496570</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>736086</t>
+          <t>947225</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>633364</t>
+          <t>886698</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>972797</t>
+          <t>1007867</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130482</t>
+          <t>136165</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207236</t>
+          <t>194354</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,17 +3484,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>135013</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110723</t>
+          <t>117995</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>160553</t>
+          <t>158556</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>305322</t>
+          <t>300859</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>258930</t>
+          <t>266689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>352994</t>
+          <t>338469</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>809476</t>
+          <t>838050</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>639536</t>
+          <t>786010</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>899085</t>
+          <t>898131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>829363</t>
+          <t>900019</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>666833</t>
+          <t>855826</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>907138</t>
+          <t>945834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1638839</t>
+          <t>1738069</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1413212</t>
+          <t>1664146</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1763702</t>
+          <t>1814915</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2025129</t>
+          <t>1901677</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1894898</t>
+          <t>1838203</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2315176</t>
+          <t>1965297</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2200273</t>
+          <t>2134905</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2067130</t>
+          <t>2082884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2462439</t>
+          <t>2190770</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4225402</t>
+          <t>4036582</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4017542</t>
+          <t>3940713</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4605931</t>
+          <t>4124839</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3426960</t>
+          <t>3496890</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3426960</t>
+          <t>3496890</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3426960</t>
+          <t>3496890</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3640222</t>
+          <t>3712440</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3640222</t>
+          <t>3712440</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3640222</t>
+          <t>3712440</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7067182</t>
+          <t>7209330</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7067182</t>
+          <t>7209330</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7067182</t>
+          <t>7209330</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
